--- a/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.90%637,000</t>
+          <t>14.95%680,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.90%</t>
+          <t>14.95%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>637000</v>
+        <v>680000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.68%706,000</t>
+          <t>4.39%706,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.39%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.39%145.5</t>
+          <t>+0.34%146</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.03%2,980,000</t>
+          <t>4.08%3,202,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2980000</v>
+        <v>3202000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.45%105</t>
+          <t>+0.95%106</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.86%3,954,000</t>
+          <t>4.07%4,427,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3954000</v>
+        <v>4427000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.79%368.5</t>
+          <t>+1.36%373.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>368.5</v>
+        <v>373.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.48%1,030,000</t>
+          <t>3.51%1,088,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1030000</v>
+        <v>1088000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.41%723</t>
+          <t>-0.97%716</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.30%482,000</t>
+          <t>3.27%517,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>482000</v>
+        <v>517000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.11%67,000</t>
+          <t>2.92%67,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.89%62,000</t>
+          <t>2.70%62,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.50%177,000</t>
+          <t>2.31%177,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.30%71,000</t>
+          <t>2.18%71,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2110</v>
+        <v>2085</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.25%114,036</t>
+          <t>2.11%114,036</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1905</v>
+        <v>251</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.14%120,000</t>
+          <t>2.02%910,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>120000</v>
+        <v>910000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>254</v>
+        <v>1885</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.02%853,000</t>
+          <t>2.00%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>853000</v>
+        <v>120000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>+4.83%1085</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2555</v>
+        <v>1085</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.81%74,000</t>
+          <t>1.78%187,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>74000</v>
+        <v>187000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:09</t>
+          <t>2026-10-02 19:05:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.99%152.5</t>
+          <t>+1.64%155</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>152.5</v>
+        <v>155</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.73%1,213,000</t>
+          <t>1.74%1,302,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1213000</v>
+        <v>1302000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1215</v>
+        <v>626</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.70%153,000</t>
+          <t>1.72%327,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>153000</v>
+        <v>327000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,34 +1480,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.73%20.3</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20.3</v>
+        <v>2540</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.69%8,783,000</t>
+          <t>1.66%74,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8783000</v>
+        <v>74000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+0.84%240</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>602</v>
+        <v>240</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.69%327,000</t>
+          <t>1.64%787,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>327000</v>
+        <v>787000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.63%238</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>238</v>
+        <v>1305</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.64%726,000</t>
+          <t>1.63%153,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>726000</v>
+        <v>153000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.62%128,000</t>
+          <t>1.59%128,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.7%1170</t>
+          <t>+0.25%20.35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1170</v>
+        <v>20.35</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.58%138,000</t>
+          <t>1.56%8,783,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>138000</v>
+        <v>8783000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1799,20 +1799,20 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>519</v>
+        <v>161.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.52%310,000</t>
+          <t>1.54%1,092,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>310000</v>
+        <v>1092000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%69.1</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>69.09999999999999</v>
+        <v>526</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.42%2,177,000</t>
+          <t>1.41%310,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2177000</v>
+        <v>310000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.83%1085</t>
+          <t>-0.43%1165</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1085</v>
+        <v>1165</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.40%143,000</t>
+          <t>1.41%138,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>143000</v>
+        <v>138000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.34%80,000</t>
+          <t>1.33%80,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1605華新</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.39%38.55</t>
+          <t>+0.87%69.7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>38.55</v>
+        <v>69.7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.22%3,375,000</t>
+          <t>1.32%2,177,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3375000</v>
+        <v>2177000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1101台泥</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.85%25.55</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>25.55</v>
+        <v>2660</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.21%4,878,000</t>
+          <t>1.26%54,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>4878000</v>
+        <v>54000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>1605華新</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.4%73.9</t>
+          <t>+0.52%38.75</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>73.90000000000001</v>
+        <v>38.75</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.16%1,657,000</t>
+          <t>1.23%3,636,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1657000</v>
+        <v>3636000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>1101台泥</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-0.78%25.35</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>161.5</v>
+        <v>25.35</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.12%766,000</t>
+          <t>1.09%4,878,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>766000</v>
+        <v>4878000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:10</t>
+          <t>2026-10-02 19:05:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.74%538</t>
+          <t>-1.62%72.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>538</v>
+        <v>72.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.11%217,000</t>
+          <t>1.07%1,657,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>217000</v>
+        <v>1657000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.08%118,000</t>
+          <t>1.04%118,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.67%3765</t>
+          <t>-0.74%538</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3765</v>
+        <v>538</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.02%29,000</t>
+          <t>1.02%217,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>29000</v>
+        <v>217000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.91%66.8</t>
+          <t>+1.2%3810</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>66.8</v>
+        <v>3810</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.02%1,589,000</t>
+          <t>0.96%29,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1589000</v>
+        <v>29000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.04%1895</t>
+          <t>+2.25%68.3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1895</v>
+        <v>68.3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.98%54,000</t>
+          <t>0.93%1,589,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>54000</v>
+        <v>1589000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2660</v>
+        <v>6290</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.97%38,000</t>
+          <t>0.92%17,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>38000</v>
+        <v>17000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-0.53%1885</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6205</v>
+        <v>1885</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.95%17,000</t>
+          <t>0.90%54,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>17000</v>
+        <v>54000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.26%48.05</t>
+          <t>0%48.05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.94%2,097,000</t>
+          <t>0.88%2,097,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.67%1480</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1480</v>
+        <v>5580</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.94%67,000</t>
+          <t>0.87%18,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>67000</v>
+        <v>18000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+9.8%1625</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5490</v>
+        <v>1625</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.93%18,000</t>
+          <t>0.87%67,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>18000</v>
+        <v>67000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1565</v>
+        <v>6800</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.83%55,000</t>
+          <t>0.78%13,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>55000</v>
+        <v>13000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6875</v>
+        <v>1510</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.83%13,000</t>
+          <t>0.75%55,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>13000</v>
+        <v>55000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.31%829</t>
+          <t>+0.72%835</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.81%102,000</t>
+          <t>0.74%102,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.74%60,000</t>
+          <t>0.67%60,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.65%933</t>
+          <t>+7.18%1000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+7.18%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>933</v>
+        <v>1000</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.66%76,000</t>
+          <t>0.62%76,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:12</t>
+          <t>2026-10-02 19:05:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.28%180</t>
+          <t>-0.56%179</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.41%243,000</t>
+          <t>0.38%243,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:13</t>
+          <t>2026-10-02 19:05:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:13</t>
+          <t>2026-10-02 19:05:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.26%18,000</t>
+          <t>0.24%18,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:13</t>
+          <t>2026-10-02 19:05:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>0%150.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.20%139,000</t>
+          <t>0.18%139,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:13</t>
+          <t>2026-10-02 19:05:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.11%1,000</t>
+          <t>0.10%1,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:13</t>
+          <t>2026-10-02 19:05:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:44</t>
+          <t>2026-10-02 22:50:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:45</t>
+          <t>2026-10-02 22:50:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:47</t>
+          <t>2026-10-02 22:50:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:48</t>
+          <t>2026-10-02 22:50:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:48</t>
+          <t>2026-10-02 22:50:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:48</t>
+          <t>2026-10-02 22:50:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:48</t>
+          <t>2026-10-02 22:50:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:48</t>
+          <t>2026-10-02 22:50:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:09</t>
+          <t>2026-10-02 22:58:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:11</t>
+          <t>2026-10-02 22:58:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:12</t>
+          <t>2026-10-02 22:58:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:13</t>
+          <t>2026-10-02 22:58:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:13</t>
+          <t>2026-10-02 22:58:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:13</t>
+          <t>2026-10-02 22:58:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:13</t>
+          <t>2026-10-02 22:58:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:13</t>
+          <t>2026-10-02 22:58:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:50</t>
+          <t>2026-10-02 23:48:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:51</t>
+          <t>2026-10-02 23:48:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:52</t>
+          <t>2026-10-02 23:48:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:54</t>
+          <t>2026-10-02 23:48:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:54</t>
+          <t>2026-10-02 23:48:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:54</t>
+          <t>2026-10-02 23:48:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:54</t>
+          <t>2026-10-02 23:48:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:54</t>
+          <t>2026-10-02 23:48:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
